--- a/database/event/7910/raw_event_7910_data.xlsx
+++ b/database/event/7910/raw_event_7910_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J151"/>
+  <dimension ref="A1:V151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,66 @@
           <t>match_baseline_rating</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>map_kpr</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>map_dpr</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>map_kast</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>map_mk_rating</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>map_swing_total</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>map_adr</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>map_rating30</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>map_kprw</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>map_swing_added</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>map_swing_given</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>map_kills</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>map_won_kills</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -507,6 +567,42 @@
       <c r="J2" t="n">
         <v>1.019</v>
       </c>
+      <c r="K2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M2" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="P2" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="S2" t="n">
+        <v>332.7</v>
+      </c>
+      <c r="T2" t="n">
+        <v>262.37</v>
+      </c>
+      <c r="U2" t="n">
+        <v>21</v>
+      </c>
+      <c r="V2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -547,6 +643,42 @@
       <c r="J3" t="n">
         <v>1.019</v>
       </c>
+      <c r="K3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M3" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="P3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="S3" t="n">
+        <v>188.64</v>
+      </c>
+      <c r="T3" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="U3" t="n">
+        <v>15</v>
+      </c>
+      <c r="V3" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -587,6 +719,42 @@
       <c r="J4" t="n">
         <v>1.019</v>
       </c>
+      <c r="K4" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M4" t="n">
+        <v>75</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="P4" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="S4" t="n">
+        <v>190.58</v>
+      </c>
+      <c r="T4" t="n">
+        <v>198.42</v>
+      </c>
+      <c r="U4" t="n">
+        <v>14</v>
+      </c>
+      <c r="V4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -627,6 +795,42 @@
       <c r="J5" t="n">
         <v>1.019</v>
       </c>
+      <c r="K5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M5" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="P5" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="S5" t="n">
+        <v>140.93</v>
+      </c>
+      <c r="T5" t="n">
+        <v>120.67</v>
+      </c>
+      <c r="U5" t="n">
+        <v>15</v>
+      </c>
+      <c r="V5" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -667,6 +871,42 @@
       <c r="J6" t="n">
         <v>1.019</v>
       </c>
+      <c r="K6" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M6" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="P6" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="S6" t="n">
+        <v>146.24</v>
+      </c>
+      <c r="T6" t="n">
+        <v>202.72</v>
+      </c>
+      <c r="U6" t="n">
+        <v>15</v>
+      </c>
+      <c r="V6" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -707,6 +947,42 @@
       <c r="J7" t="n">
         <v>1.019</v>
       </c>
+      <c r="K7" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M7" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P7" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.091</v>
+      </c>
+      <c r="S7" t="n">
+        <v>224.36</v>
+      </c>
+      <c r="T7" t="n">
+        <v>196.06</v>
+      </c>
+      <c r="U7" t="n">
+        <v>17</v>
+      </c>
+      <c r="V7" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -747,6 +1023,42 @@
       <c r="J8" t="n">
         <v>1.019</v>
       </c>
+      <c r="K8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M8" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="P8" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.182</v>
+      </c>
+      <c r="S8" t="n">
+        <v>150.48</v>
+      </c>
+      <c r="T8" t="n">
+        <v>190.95</v>
+      </c>
+      <c r="U8" t="n">
+        <v>18</v>
+      </c>
+      <c r="V8" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -787,6 +1099,42 @@
       <c r="J9" t="n">
         <v>1.019</v>
       </c>
+      <c r="K9" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M9" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="P9" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>220.25</v>
+      </c>
+      <c r="T9" t="n">
+        <v>225.27</v>
+      </c>
+      <c r="U9" t="n">
+        <v>14</v>
+      </c>
+      <c r="V9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -827,6 +1175,42 @@
       <c r="J10" t="n">
         <v>1.019</v>
       </c>
+      <c r="K10" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="P10" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="S10" t="n">
+        <v>111.65</v>
+      </c>
+      <c r="T10" t="n">
+        <v>173.79</v>
+      </c>
+      <c r="U10" t="n">
+        <v>11</v>
+      </c>
+      <c r="V10" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -867,6 +1251,42 @@
       <c r="J11" t="n">
         <v>1.019</v>
       </c>
+      <c r="K11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M11" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="P11" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="S11" t="n">
+        <v>192.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>213.02</v>
+      </c>
+      <c r="U11" t="n">
+        <v>8</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -907,6 +1327,42 @@
       <c r="J12" t="n">
         <v>1.064</v>
       </c>
+      <c r="K12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M12" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="P12" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="S12" t="n">
+        <v>396.28</v>
+      </c>
+      <c r="T12" t="n">
+        <v>300.1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>30</v>
+      </c>
+      <c r="V12" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -947,6 +1403,42 @@
       <c r="J13" t="n">
         <v>1.064</v>
       </c>
+      <c r="K13" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M13" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="P13" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="S13" t="n">
+        <v>351.65</v>
+      </c>
+      <c r="T13" t="n">
+        <v>343.5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>22</v>
+      </c>
+      <c r="V13" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -987,6 +1479,42 @@
       <c r="J14" t="n">
         <v>1.064</v>
       </c>
+      <c r="K14" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="P14" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="S14" t="n">
+        <v>335.22</v>
+      </c>
+      <c r="T14" t="n">
+        <v>367.41</v>
+      </c>
+      <c r="U14" t="n">
+        <v>17</v>
+      </c>
+      <c r="V14" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1027,6 +1555,42 @@
       <c r="J15" t="n">
         <v>1.064</v>
       </c>
+      <c r="K15" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M15" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="P15" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="S15" t="n">
+        <v>296.8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>291.73</v>
+      </c>
+      <c r="U15" t="n">
+        <v>22</v>
+      </c>
+      <c r="V15" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1067,6 +1631,42 @@
       <c r="J16" t="n">
         <v>1.064</v>
       </c>
+      <c r="K16" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M16" t="n">
+        <v>69</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P16" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="S16" t="n">
+        <v>325.23</v>
+      </c>
+      <c r="T16" t="n">
+        <v>271.58</v>
+      </c>
+      <c r="U16" t="n">
+        <v>15</v>
+      </c>
+      <c r="V16" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1107,6 +1707,42 @@
       <c r="J17" t="n">
         <v>1.064</v>
       </c>
+      <c r="K17" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M17" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P17" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.462</v>
+      </c>
+      <c r="S17" t="n">
+        <v>385.44</v>
+      </c>
+      <c r="T17" t="n">
+        <v>347.98</v>
+      </c>
+      <c r="U17" t="n">
+        <v>20</v>
+      </c>
+      <c r="V17" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1147,6 +1783,42 @@
       <c r="J18" t="n">
         <v>1.064</v>
       </c>
+      <c r="K18" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M18" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="P18" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="S18" t="n">
+        <v>337.21</v>
+      </c>
+      <c r="T18" t="n">
+        <v>379.56</v>
+      </c>
+      <c r="U18" t="n">
+        <v>18</v>
+      </c>
+      <c r="V18" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1187,6 +1859,42 @@
       <c r="J19" t="n">
         <v>1.064</v>
       </c>
+      <c r="K19" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M19" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="P19" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="S19" t="n">
+        <v>294.04</v>
+      </c>
+      <c r="T19" t="n">
+        <v>323.93</v>
+      </c>
+      <c r="U19" t="n">
+        <v>19</v>
+      </c>
+      <c r="V19" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1227,6 +1935,42 @@
       <c r="J20" t="n">
         <v>1.064</v>
       </c>
+      <c r="K20" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M20" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="P20" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="S20" t="n">
+        <v>317.09</v>
+      </c>
+      <c r="T20" t="n">
+        <v>339.39</v>
+      </c>
+      <c r="U20" t="n">
+        <v>19</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1267,6 +2011,42 @@
       <c r="J21" t="n">
         <v>1.064</v>
       </c>
+      <c r="K21" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M21" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="P21" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="S21" t="n">
+        <v>229.27</v>
+      </c>
+      <c r="T21" t="n">
+        <v>314.33</v>
+      </c>
+      <c r="U21" t="n">
+        <v>13</v>
+      </c>
+      <c r="V21" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1307,6 +2087,42 @@
       <c r="J22" t="n">
         <v>1.089</v>
       </c>
+      <c r="K22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M22" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="P22" t="n">
+        <v>143.4</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.385</v>
+      </c>
+      <c r="S22" t="n">
+        <v>432.25</v>
+      </c>
+      <c r="T22" t="n">
+        <v>165.2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>23</v>
+      </c>
+      <c r="V22" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1347,6 +2163,42 @@
       <c r="J23" t="n">
         <v>1.089</v>
       </c>
+      <c r="K23" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="M23" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="P23" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="S23" t="n">
+        <v>165.44</v>
+      </c>
+      <c r="T23" t="n">
+        <v>146.78</v>
+      </c>
+      <c r="U23" t="n">
+        <v>13</v>
+      </c>
+      <c r="V23" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1387,6 +2239,42 @@
       <c r="J24" t="n">
         <v>1.089</v>
       </c>
+      <c r="K24" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M24" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P24" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="S24" t="n">
+        <v>225.52</v>
+      </c>
+      <c r="T24" t="n">
+        <v>179.04</v>
+      </c>
+      <c r="U24" t="n">
+        <v>11</v>
+      </c>
+      <c r="V24" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1427,6 +2315,42 @@
       <c r="J25" t="n">
         <v>1.089</v>
       </c>
+      <c r="K25" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M25" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="P25" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="S25" t="n">
+        <v>136.76</v>
+      </c>
+      <c r="T25" t="n">
+        <v>137.42</v>
+      </c>
+      <c r="U25" t="n">
+        <v>11</v>
+      </c>
+      <c r="V25" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1467,6 +2391,42 @@
       <c r="J26" t="n">
         <v>1.089</v>
       </c>
+      <c r="K26" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M26" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="P26" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="S26" t="n">
+        <v>113.44</v>
+      </c>
+      <c r="T26" t="n">
+        <v>176.57</v>
+      </c>
+      <c r="U26" t="n">
+        <v>15</v>
+      </c>
+      <c r="V26" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1507,6 +2467,42 @@
       <c r="J27" t="n">
         <v>1.089</v>
       </c>
+      <c r="K27" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M27" t="n">
+        <v>50</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-2.56</v>
+      </c>
+      <c r="P27" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>213.2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>259.21</v>
+      </c>
+      <c r="U27" t="n">
+        <v>11</v>
+      </c>
+      <c r="V27" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1547,6 +2543,42 @@
       <c r="J28" t="n">
         <v>1.089</v>
       </c>
+      <c r="K28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M28" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="P28" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>186.97</v>
+      </c>
+      <c r="T28" t="n">
+        <v>150.87</v>
+      </c>
+      <c r="U28" t="n">
+        <v>10</v>
+      </c>
+      <c r="V28" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1587,6 +2619,42 @@
       <c r="J29" t="n">
         <v>1.089</v>
       </c>
+      <c r="K29" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M29" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S29" t="n">
+        <v>138.34</v>
+      </c>
+      <c r="T29" t="n">
+        <v>194.12</v>
+      </c>
+      <c r="U29" t="n">
+        <v>9</v>
+      </c>
+      <c r="V29" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1627,6 +2695,42 @@
       <c r="J30" t="n">
         <v>1.089</v>
       </c>
+      <c r="K30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M30" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="P30" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="n">
+        <v>165.22</v>
+      </c>
+      <c r="T30" t="n">
+        <v>213.51</v>
+      </c>
+      <c r="U30" t="n">
+        <v>9</v>
+      </c>
+      <c r="V30" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1667,6 +2771,42 @@
       <c r="J31" t="n">
         <v>1.089</v>
       </c>
+      <c r="K31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M31" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-8.58</v>
+      </c>
+      <c r="P31" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S31" t="n">
+        <v>101.33</v>
+      </c>
+      <c r="T31" t="n">
+        <v>255.72</v>
+      </c>
+      <c r="U31" t="n">
+        <v>9</v>
+      </c>
+      <c r="V31" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1707,6 +2847,42 @@
       <c r="J32" t="n">
         <v>1.096</v>
       </c>
+      <c r="K32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M32" t="n">
+        <v>80</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P32" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="S32" t="n">
+        <v>312.48</v>
+      </c>
+      <c r="T32" t="n">
+        <v>248.57</v>
+      </c>
+      <c r="U32" t="n">
+        <v>18</v>
+      </c>
+      <c r="V32" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1747,6 +2923,42 @@
       <c r="J33" t="n">
         <v>1.096</v>
       </c>
+      <c r="K33" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M33" t="n">
+        <v>70</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="P33" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="S33" t="n">
+        <v>271.67</v>
+      </c>
+      <c r="T33" t="n">
+        <v>228.26</v>
+      </c>
+      <c r="U33" t="n">
+        <v>15</v>
+      </c>
+      <c r="V33" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1787,6 +2999,42 @@
       <c r="J34" t="n">
         <v>1.096</v>
       </c>
+      <c r="K34" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M34" t="n">
+        <v>80</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="P34" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="S34" t="n">
+        <v>191.79</v>
+      </c>
+      <c r="T34" t="n">
+        <v>232.09</v>
+      </c>
+      <c r="U34" t="n">
+        <v>14</v>
+      </c>
+      <c r="V34" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1827,6 +3075,42 @@
       <c r="J35" t="n">
         <v>1.096</v>
       </c>
+      <c r="K35" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M35" t="n">
+        <v>70</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O35" t="n">
+        <v>-8.41</v>
+      </c>
+      <c r="P35" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="n">
+        <v>189.18</v>
+      </c>
+      <c r="T35" t="n">
+        <v>357.43</v>
+      </c>
+      <c r="U35" t="n">
+        <v>13</v>
+      </c>
+      <c r="V35" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1867,6 +3151,42 @@
       <c r="J36" t="n">
         <v>1.096</v>
       </c>
+      <c r="K36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M36" t="n">
+        <v>70</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="O36" t="n">
+        <v>-9.119999999999999</v>
+      </c>
+      <c r="P36" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="S36" t="n">
+        <v>132.62</v>
+      </c>
+      <c r="T36" t="n">
+        <v>315.06</v>
+      </c>
+      <c r="U36" t="n">
+        <v>8</v>
+      </c>
+      <c r="V36" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1907,6 +3227,42 @@
       <c r="J37" t="n">
         <v>1.096</v>
       </c>
+      <c r="K37" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M37" t="n">
+        <v>70</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="O37" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="P37" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="S37" t="n">
+        <v>271.9</v>
+      </c>
+      <c r="T37" t="n">
+        <v>170.96</v>
+      </c>
+      <c r="U37" t="n">
+        <v>19</v>
+      </c>
+      <c r="V37" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1947,6 +3303,42 @@
       <c r="J38" t="n">
         <v>1.096</v>
       </c>
+      <c r="K38" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M38" t="n">
+        <v>65</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="O38" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="P38" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="S38" t="n">
+        <v>316.55</v>
+      </c>
+      <c r="T38" t="n">
+        <v>227.55</v>
+      </c>
+      <c r="U38" t="n">
+        <v>17</v>
+      </c>
+      <c r="V38" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1987,6 +3379,42 @@
       <c r="J39" t="n">
         <v>1.096</v>
       </c>
+      <c r="K39" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M39" t="n">
+        <v>80</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="O39" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="P39" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" t="n">
+        <v>314.73</v>
+      </c>
+      <c r="T39" t="n">
+        <v>232.65</v>
+      </c>
+      <c r="U39" t="n">
+        <v>14</v>
+      </c>
+      <c r="V39" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2027,6 +3455,42 @@
       <c r="J40" t="n">
         <v>1.096</v>
       </c>
+      <c r="K40" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M40" t="n">
+        <v>75</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="P40" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="S40" t="n">
+        <v>277.78</v>
+      </c>
+      <c r="T40" t="n">
+        <v>211.58</v>
+      </c>
+      <c r="U40" t="n">
+        <v>12</v>
+      </c>
+      <c r="V40" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2067,6 +3531,42 @@
       <c r="J41" t="n">
         <v>1.096</v>
       </c>
+      <c r="K41" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M41" t="n">
+        <v>65</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="O41" t="n">
+        <v>-2.73</v>
+      </c>
+      <c r="P41" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="S41" t="n">
+        <v>200.42</v>
+      </c>
+      <c r="T41" t="n">
+        <v>254.99</v>
+      </c>
+      <c r="U41" t="n">
+        <v>11</v>
+      </c>
+      <c r="V41" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2107,6 +3607,42 @@
       <c r="J42" t="n">
         <v>1.057</v>
       </c>
+      <c r="K42" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M42" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="P42" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="S42" t="n">
+        <v>296.21</v>
+      </c>
+      <c r="T42" t="n">
+        <v>231.91</v>
+      </c>
+      <c r="U42" t="n">
+        <v>17</v>
+      </c>
+      <c r="V42" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2147,6 +3683,42 @@
       <c r="J43" t="n">
         <v>1.057</v>
       </c>
+      <c r="K43" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M43" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P43" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.273</v>
+      </c>
+      <c r="S43" t="n">
+        <v>322.78</v>
+      </c>
+      <c r="T43" t="n">
+        <v>288.88</v>
+      </c>
+      <c r="U43" t="n">
+        <v>16</v>
+      </c>
+      <c r="V43" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2187,6 +3759,42 @@
       <c r="J44" t="n">
         <v>1.057</v>
       </c>
+      <c r="K44" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M44" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P44" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="S44" t="n">
+        <v>285</v>
+      </c>
+      <c r="T44" t="n">
+        <v>247.65</v>
+      </c>
+      <c r="U44" t="n">
+        <v>17</v>
+      </c>
+      <c r="V44" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2227,6 +3835,42 @@
       <c r="J45" t="n">
         <v>1.057</v>
       </c>
+      <c r="K45" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M45" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="O45" t="n">
+        <v>-3.09</v>
+      </c>
+      <c r="P45" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="S45" t="n">
+        <v>208.56</v>
+      </c>
+      <c r="T45" t="n">
+        <v>282.82</v>
+      </c>
+      <c r="U45" t="n">
+        <v>16</v>
+      </c>
+      <c r="V45" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2267,6 +3911,42 @@
       <c r="J46" t="n">
         <v>1.057</v>
       </c>
+      <c r="K46" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M46" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="O46" t="n">
+        <v>-6.11</v>
+      </c>
+      <c r="P46" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="S46" t="n">
+        <v>207.97</v>
+      </c>
+      <c r="T46" t="n">
+        <v>354.66</v>
+      </c>
+      <c r="U46" t="n">
+        <v>8</v>
+      </c>
+      <c r="V46" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2307,6 +3987,42 @@
       <c r="J47" t="n">
         <v>1.057</v>
       </c>
+      <c r="K47" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M47" t="n">
+        <v>75</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O47" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="P47" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="S47" t="n">
+        <v>342.27</v>
+      </c>
+      <c r="T47" t="n">
+        <v>293.96</v>
+      </c>
+      <c r="U47" t="n">
+        <v>22</v>
+      </c>
+      <c r="V47" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2347,6 +4063,42 @@
       <c r="J48" t="n">
         <v>1.057</v>
       </c>
+      <c r="K48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M48" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O48" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="P48" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.462</v>
+      </c>
+      <c r="S48" t="n">
+        <v>262.45</v>
+      </c>
+      <c r="T48" t="n">
+        <v>286.3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>25</v>
+      </c>
+      <c r="V48" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2387,6 +4139,42 @@
       <c r="J49" t="n">
         <v>1.057</v>
       </c>
+      <c r="K49" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M49" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="O49" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="P49" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="S49" t="n">
+        <v>270.32</v>
+      </c>
+      <c r="T49" t="n">
+        <v>168.85</v>
+      </c>
+      <c r="U49" t="n">
+        <v>15</v>
+      </c>
+      <c r="V49" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2427,6 +4215,42 @@
       <c r="J50" t="n">
         <v>1.057</v>
       </c>
+      <c r="K50" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M50" t="n">
+        <v>75</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="O50" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="P50" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="S50" t="n">
+        <v>294.28</v>
+      </c>
+      <c r="T50" t="n">
+        <v>297.64</v>
+      </c>
+      <c r="U50" t="n">
+        <v>14</v>
+      </c>
+      <c r="V50" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2467,6 +4291,42 @@
       <c r="J51" t="n">
         <v>1.057</v>
       </c>
+      <c r="K51" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M51" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="O51" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="P51" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="S51" t="n">
+        <v>236.53</v>
+      </c>
+      <c r="T51" t="n">
+        <v>273.79</v>
+      </c>
+      <c r="U51" t="n">
+        <v>14</v>
+      </c>
+      <c r="V51" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2507,6 +4367,42 @@
       <c r="J52" t="n">
         <v>1.041</v>
       </c>
+      <c r="K52" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M52" t="n">
+        <v>60</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="O52" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="P52" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="S52" t="n">
+        <v>436.05</v>
+      </c>
+      <c r="T52" t="n">
+        <v>322.61</v>
+      </c>
+      <c r="U52" t="n">
+        <v>22</v>
+      </c>
+      <c r="V52" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2547,6 +4443,42 @@
       <c r="J53" t="n">
         <v>1.041</v>
       </c>
+      <c r="K53" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M53" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="O53" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="S53" t="n">
+        <v>257.74</v>
+      </c>
+      <c r="T53" t="n">
+        <v>257.86</v>
+      </c>
+      <c r="U53" t="n">
+        <v>19</v>
+      </c>
+      <c r="V53" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2587,6 +4519,42 @@
       <c r="J54" t="n">
         <v>1.041</v>
       </c>
+      <c r="K54" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M54" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="O54" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="P54" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="S54" t="n">
+        <v>252.71</v>
+      </c>
+      <c r="T54" t="n">
+        <v>275.33</v>
+      </c>
+      <c r="U54" t="n">
+        <v>18</v>
+      </c>
+      <c r="V54" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2627,6 +4595,42 @@
       <c r="J55" t="n">
         <v>1.041</v>
       </c>
+      <c r="K55" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M55" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="O55" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="P55" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="S55" t="n">
+        <v>313.82</v>
+      </c>
+      <c r="T55" t="n">
+        <v>324.14</v>
+      </c>
+      <c r="U55" t="n">
+        <v>14</v>
+      </c>
+      <c r="V55" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2667,6 +4671,42 @@
       <c r="J56" t="n">
         <v>1.041</v>
       </c>
+      <c r="K56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M56" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="O56" t="n">
+        <v>-3.93</v>
+      </c>
+      <c r="P56" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="S56" t="n">
+        <v>274.17</v>
+      </c>
+      <c r="T56" t="n">
+        <v>392.14</v>
+      </c>
+      <c r="U56" t="n">
+        <v>14</v>
+      </c>
+      <c r="V56" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2707,6 +4747,42 @@
       <c r="J57" t="n">
         <v>1.041</v>
       </c>
+      <c r="K57" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M57" t="n">
+        <v>80</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O57" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P57" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="S57" t="n">
+        <v>380.19</v>
+      </c>
+      <c r="T57" t="n">
+        <v>300.34</v>
+      </c>
+      <c r="U57" t="n">
+        <v>28</v>
+      </c>
+      <c r="V57" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2747,6 +4823,42 @@
       <c r="J58" t="n">
         <v>1.041</v>
       </c>
+      <c r="K58" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M58" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P58" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="S58" t="n">
+        <v>307.88</v>
+      </c>
+      <c r="T58" t="n">
+        <v>300.38</v>
+      </c>
+      <c r="U58" t="n">
+        <v>27</v>
+      </c>
+      <c r="V58" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2787,6 +4899,42 @@
       <c r="J59" t="n">
         <v>1.041</v>
       </c>
+      <c r="K59" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M59" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="P59" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S59" t="n">
+        <v>340.55</v>
+      </c>
+      <c r="T59" t="n">
+        <v>329.73</v>
+      </c>
+      <c r="U59" t="n">
+        <v>19</v>
+      </c>
+      <c r="V59" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2827,6 +4975,42 @@
       <c r="J60" t="n">
         <v>1.041</v>
       </c>
+      <c r="K60" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M60" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="N60" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P60" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="S60" t="n">
+        <v>266.42</v>
+      </c>
+      <c r="T60" t="n">
+        <v>258.96</v>
+      </c>
+      <c r="U60" t="n">
+        <v>23</v>
+      </c>
+      <c r="V60" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2867,6 +5051,42 @@
       <c r="J61" t="n">
         <v>1.041</v>
       </c>
+      <c r="K61" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M61" t="n">
+        <v>70</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="O61" t="n">
+        <v>-2.69</v>
+      </c>
+      <c r="P61" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="S61" t="n">
+        <v>264.56</v>
+      </c>
+      <c r="T61" t="n">
+        <v>345.14</v>
+      </c>
+      <c r="U61" t="n">
+        <v>13</v>
+      </c>
+      <c r="V61" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2907,6 +5127,42 @@
       <c r="J62" t="n">
         <v>1.101</v>
       </c>
+      <c r="K62" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M62" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P62" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S62" t="n">
+        <v>265.19</v>
+      </c>
+      <c r="T62" t="n">
+        <v>253.29</v>
+      </c>
+      <c r="U62" t="n">
+        <v>12</v>
+      </c>
+      <c r="V62" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2947,6 +5203,42 @@
       <c r="J63" t="n">
         <v>1.101</v>
       </c>
+      <c r="K63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M63" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O63" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="P63" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S63" t="n">
+        <v>164.62</v>
+      </c>
+      <c r="T63" t="n">
+        <v>175.62</v>
+      </c>
+      <c r="U63" t="n">
+        <v>9</v>
+      </c>
+      <c r="V63" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2987,6 +5279,42 @@
       <c r="J64" t="n">
         <v>1.101</v>
       </c>
+      <c r="K64" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M64" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="O64" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="P64" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S64" t="n">
+        <v>115.91</v>
+      </c>
+      <c r="T64" t="n">
+        <v>120.97</v>
+      </c>
+      <c r="U64" t="n">
+        <v>11</v>
+      </c>
+      <c r="V64" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3027,6 +5355,42 @@
       <c r="J65" t="n">
         <v>1.101</v>
       </c>
+      <c r="K65" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M65" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="O65" t="n">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="P65" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S65" t="n">
+        <v>105.08</v>
+      </c>
+      <c r="T65" t="n">
+        <v>253.04</v>
+      </c>
+      <c r="U65" t="n">
+        <v>10</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3067,6 +5431,42 @@
       <c r="J66" t="n">
         <v>1.101</v>
       </c>
+      <c r="K66" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M66" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O66" t="n">
+        <v>-11.07</v>
+      </c>
+      <c r="P66" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S66" t="n">
+        <v>90.05</v>
+      </c>
+      <c r="T66" t="n">
+        <v>289.32</v>
+      </c>
+      <c r="U66" t="n">
+        <v>8</v>
+      </c>
+      <c r="V66" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3107,6 +5507,42 @@
       <c r="J67" t="n">
         <v>1.101</v>
       </c>
+      <c r="K67" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M67" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="N67" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="O67" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="P67" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="S67" t="n">
+        <v>380.53</v>
+      </c>
+      <c r="T67" t="n">
+        <v>80.98</v>
+      </c>
+      <c r="U67" t="n">
+        <v>20</v>
+      </c>
+      <c r="V67" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3147,6 +5583,42 @@
       <c r="J68" t="n">
         <v>1.101</v>
       </c>
+      <c r="K68" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M68" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="N68" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="O68" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="P68" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="S68" t="n">
+        <v>257.92</v>
+      </c>
+      <c r="T68" t="n">
+        <v>146.38</v>
+      </c>
+      <c r="U68" t="n">
+        <v>16</v>
+      </c>
+      <c r="V68" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3187,6 +5659,42 @@
       <c r="J69" t="n">
         <v>1.101</v>
       </c>
+      <c r="K69" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M69" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="O69" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="P69" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1</v>
+      </c>
+      <c r="S69" t="n">
+        <v>155.17</v>
+      </c>
+      <c r="T69" t="n">
+        <v>188.02</v>
+      </c>
+      <c r="U69" t="n">
+        <v>15</v>
+      </c>
+      <c r="V69" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3227,6 +5735,42 @@
       <c r="J70" t="n">
         <v>1.101</v>
       </c>
+      <c r="K70" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M70" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="O70" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="P70" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="S70" t="n">
+        <v>157.34</v>
+      </c>
+      <c r="T70" t="n">
+        <v>186.56</v>
+      </c>
+      <c r="U70" t="n">
+        <v>13</v>
+      </c>
+      <c r="V70" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3267,6 +5811,42 @@
       <c r="J71" t="n">
         <v>1.101</v>
       </c>
+      <c r="K71" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M71" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O71" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="P71" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="S71" t="n">
+        <v>132.65</v>
+      </c>
+      <c r="T71" t="n">
+        <v>138.91</v>
+      </c>
+      <c r="U71" t="n">
+        <v>9</v>
+      </c>
+      <c r="V71" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3305,7 +5885,43 @@
         <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>1.072</v>
+        <v>1.073</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M72" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="O72" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="P72" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="S72" t="n">
+        <v>297.49</v>
+      </c>
+      <c r="T72" t="n">
+        <v>178.83</v>
+      </c>
+      <c r="U72" t="n">
+        <v>20</v>
+      </c>
+      <c r="V72" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="73">
@@ -3345,7 +5961,43 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>1.072</v>
+        <v>1.073</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M73" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="N73" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O73" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="P73" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1.385</v>
+      </c>
+      <c r="S73" t="n">
+        <v>364.02</v>
+      </c>
+      <c r="T73" t="n">
+        <v>294.14</v>
+      </c>
+      <c r="U73" t="n">
+        <v>23</v>
+      </c>
+      <c r="V73" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="74">
@@ -3385,7 +6037,43 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>1.072</v>
+        <v>1.073</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M74" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="O74" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="P74" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="S74" t="n">
+        <v>261.06</v>
+      </c>
+      <c r="T74" t="n">
+        <v>184.54</v>
+      </c>
+      <c r="U74" t="n">
+        <v>11</v>
+      </c>
+      <c r="V74" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="75">
@@ -3425,7 +6113,43 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>1.072</v>
+        <v>1.073</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M75" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="P75" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="S75" t="n">
+        <v>242.07</v>
+      </c>
+      <c r="T75" t="n">
+        <v>241.14</v>
+      </c>
+      <c r="U75" t="n">
+        <v>13</v>
+      </c>
+      <c r="V75" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="76">
@@ -3465,7 +6189,43 @@
         <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>1.072</v>
+        <v>1.073</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M76" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O76" t="n">
+        <v>-7.02</v>
+      </c>
+      <c r="P76" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="S76" t="n">
+        <v>192.13</v>
+      </c>
+      <c r="T76" t="n">
+        <v>353.55</v>
+      </c>
+      <c r="U76" t="n">
+        <v>9</v>
+      </c>
+      <c r="V76" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="77">
@@ -3499,13 +6259,49 @@
         <v>1.56</v>
       </c>
       <c r="H77" t="n">
-        <v>1.066</v>
+        <v>1.068</v>
       </c>
       <c r="I77" t="n">
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>1.072</v>
+        <v>1.073</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M77" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="N77" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="O77" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="P77" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S77" t="n">
+        <v>348.32</v>
+      </c>
+      <c r="T77" t="n">
+        <v>164.94</v>
+      </c>
+      <c r="U77" t="n">
+        <v>18</v>
+      </c>
+      <c r="V77" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="78">
@@ -3539,13 +6335,49 @@
         <v>1.13</v>
       </c>
       <c r="H78" t="n">
-        <v>1.066</v>
+        <v>1.068</v>
       </c>
       <c r="I78" t="n">
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>1.072</v>
+        <v>1.073</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M78" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="N78" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O78" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="P78" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="R78" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S78" t="n">
+        <v>274.89</v>
+      </c>
+      <c r="T78" t="n">
+        <v>322.43</v>
+      </c>
+      <c r="U78" t="n">
+        <v>17</v>
+      </c>
+      <c r="V78" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="79">
@@ -3579,13 +6411,49 @@
         <v>1.13</v>
       </c>
       <c r="H79" t="n">
-        <v>1.066</v>
+        <v>1.068</v>
       </c>
       <c r="I79" t="n">
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>1.072</v>
+        <v>1.073</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M79" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="N79" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="P79" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S79" t="n">
+        <v>254.48</v>
+      </c>
+      <c r="T79" t="n">
+        <v>247.67</v>
+      </c>
+      <c r="U79" t="n">
+        <v>17</v>
+      </c>
+      <c r="V79" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="80">
@@ -3616,16 +6484,52 @@
         <v>-3</v>
       </c>
       <c r="G80" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H80" t="n">
-        <v>1.066</v>
+        <v>1.068</v>
       </c>
       <c r="I80" t="n">
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>1.072</v>
+        <v>1.073</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M80" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="N80" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="O80" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="P80" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S80" t="n">
+        <v>196.44</v>
+      </c>
+      <c r="T80" t="n">
+        <v>253.69</v>
+      </c>
+      <c r="U80" t="n">
+        <v>11</v>
+      </c>
+      <c r="V80" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="81">
@@ -3659,13 +6563,49 @@
         <v>0.71</v>
       </c>
       <c r="H81" t="n">
-        <v>1.066</v>
+        <v>1.068</v>
       </c>
       <c r="I81" t="n">
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>1.072</v>
+        <v>1.073</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M81" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="O81" t="n">
+        <v>-8.26</v>
+      </c>
+      <c r="P81" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S81" t="n">
+        <v>178.08</v>
+      </c>
+      <c r="T81" t="n">
+        <v>368.03</v>
+      </c>
+      <c r="U81" t="n">
+        <v>15</v>
+      </c>
+      <c r="V81" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="82">
@@ -3707,6 +6647,42 @@
       <c r="J82" t="n">
         <v>1.098</v>
       </c>
+      <c r="K82" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M82" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="N82" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="O82" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="P82" t="n">
+        <v>131.8</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R82" t="n">
+        <v>1.462</v>
+      </c>
+      <c r="S82" t="n">
+        <v>295.8</v>
+      </c>
+      <c r="T82" t="n">
+        <v>138.14</v>
+      </c>
+      <c r="U82" t="n">
+        <v>20</v>
+      </c>
+      <c r="V82" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3747,6 +6723,42 @@
       <c r="J83" t="n">
         <v>1.098</v>
       </c>
+      <c r="K83" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M83" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="N83" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="O83" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="P83" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R83" t="n">
+        <v>1</v>
+      </c>
+      <c r="S83" t="n">
+        <v>274.58</v>
+      </c>
+      <c r="T83" t="n">
+        <v>113.01</v>
+      </c>
+      <c r="U83" t="n">
+        <v>16</v>
+      </c>
+      <c r="V83" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3787,6 +6799,42 @@
       <c r="J84" t="n">
         <v>1.098</v>
       </c>
+      <c r="K84" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M84" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="P84" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="S84" t="n">
+        <v>139.92</v>
+      </c>
+      <c r="T84" t="n">
+        <v>108.56</v>
+      </c>
+      <c r="U84" t="n">
+        <v>12</v>
+      </c>
+      <c r="V84" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3827,6 +6875,42 @@
       <c r="J85" t="n">
         <v>1.098</v>
       </c>
+      <c r="K85" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M85" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="P85" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="S85" t="n">
+        <v>114.87</v>
+      </c>
+      <c r="T85" t="n">
+        <v>110.74</v>
+      </c>
+      <c r="U85" t="n">
+        <v>8</v>
+      </c>
+      <c r="V85" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3867,6 +6951,42 @@
       <c r="J86" t="n">
         <v>1.098</v>
       </c>
+      <c r="K86" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M86" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="O86" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="P86" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="S86" t="n">
+        <v>132.9</v>
+      </c>
+      <c r="T86" t="n">
+        <v>175.06</v>
+      </c>
+      <c r="U86" t="n">
+        <v>9</v>
+      </c>
+      <c r="V86" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3907,6 +7027,42 @@
       <c r="J87" t="n">
         <v>1.098</v>
       </c>
+      <c r="K87" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M87" t="n">
+        <v>75</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O87" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="P87" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R87" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="S87" t="n">
+        <v>265.35</v>
+      </c>
+      <c r="T87" t="n">
+        <v>177</v>
+      </c>
+      <c r="U87" t="n">
+        <v>16</v>
+      </c>
+      <c r="V87" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3947,6 +7103,42 @@
       <c r="J88" t="n">
         <v>1.098</v>
       </c>
+      <c r="K88" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M88" t="n">
+        <v>50</v>
+      </c>
+      <c r="N88" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O88" t="n">
+        <v>-4.91</v>
+      </c>
+      <c r="P88" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R88" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="S88" t="n">
+        <v>110.57</v>
+      </c>
+      <c r="T88" t="n">
+        <v>189.09</v>
+      </c>
+      <c r="U88" t="n">
+        <v>8</v>
+      </c>
+      <c r="V88" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3987,6 +7179,42 @@
       <c r="J89" t="n">
         <v>1.098</v>
       </c>
+      <c r="K89" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M89" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O89" t="n">
+        <v>-4.03</v>
+      </c>
+      <c r="P89" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>105.62</v>
+      </c>
+      <c r="T89" t="n">
+        <v>170.02</v>
+      </c>
+      <c r="U89" t="n">
+        <v>5</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4027,6 +7255,42 @@
       <c r="J90" t="n">
         <v>1.098</v>
       </c>
+      <c r="K90" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M90" t="n">
+        <v>50</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O90" t="n">
+        <v>-8.16</v>
+      </c>
+      <c r="P90" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="S90" t="n">
+        <v>114.66</v>
+      </c>
+      <c r="T90" t="n">
+        <v>245.28</v>
+      </c>
+      <c r="U90" t="n">
+        <v>8</v>
+      </c>
+      <c r="V90" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4067,6 +7331,42 @@
       <c r="J91" t="n">
         <v>1.098</v>
       </c>
+      <c r="K91" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M91" t="n">
+        <v>50</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>-7.96</v>
+      </c>
+      <c r="P91" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="S91" t="n">
+        <v>49.27</v>
+      </c>
+      <c r="T91" t="n">
+        <v>176.62</v>
+      </c>
+      <c r="U91" t="n">
+        <v>2</v>
+      </c>
+      <c r="V91" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4107,6 +7407,42 @@
       <c r="J92" t="n">
         <v>1.048</v>
       </c>
+      <c r="K92" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M92" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="N92" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="O92" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P92" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="R92" t="n">
+        <v>1</v>
+      </c>
+      <c r="S92" t="n">
+        <v>368.99</v>
+      </c>
+      <c r="T92" t="n">
+        <v>261.55</v>
+      </c>
+      <c r="U92" t="n">
+        <v>22</v>
+      </c>
+      <c r="V92" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4147,6 +7483,42 @@
       <c r="J93" t="n">
         <v>1.048</v>
       </c>
+      <c r="K93" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M93" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="N93" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O93" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P93" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R93" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="S93" t="n">
+        <v>303.47</v>
+      </c>
+      <c r="T93" t="n">
+        <v>253.46</v>
+      </c>
+      <c r="U93" t="n">
+        <v>25</v>
+      </c>
+      <c r="V93" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4187,6 +7559,42 @@
       <c r="J94" t="n">
         <v>1.048</v>
       </c>
+      <c r="K94" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M94" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="N94" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="O94" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="P94" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="R94" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="S94" t="n">
+        <v>294.04</v>
+      </c>
+      <c r="T94" t="n">
+        <v>337.7</v>
+      </c>
+      <c r="U94" t="n">
+        <v>25</v>
+      </c>
+      <c r="V94" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4227,6 +7635,42 @@
       <c r="J95" t="n">
         <v>1.048</v>
       </c>
+      <c r="K95" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M95" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="O95" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="P95" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S95" t="n">
+        <v>301.6</v>
+      </c>
+      <c r="T95" t="n">
+        <v>305.08</v>
+      </c>
+      <c r="U95" t="n">
+        <v>20</v>
+      </c>
+      <c r="V95" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4267,6 +7711,42 @@
       <c r="J96" t="n">
         <v>1.048</v>
       </c>
+      <c r="K96" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M96" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="O96" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="P96" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="S96" t="n">
+        <v>257.95</v>
+      </c>
+      <c r="T96" t="n">
+        <v>275.7</v>
+      </c>
+      <c r="U96" t="n">
+        <v>16</v>
+      </c>
+      <c r="V96" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4307,6 +7787,42 @@
       <c r="J97" t="n">
         <v>1.048</v>
       </c>
+      <c r="K97" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M97" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="N97" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O97" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="P97" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R97" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="S97" t="n">
+        <v>415.21</v>
+      </c>
+      <c r="T97" t="n">
+        <v>268.44</v>
+      </c>
+      <c r="U97" t="n">
+        <v>22</v>
+      </c>
+      <c r="V97" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4347,6 +7863,42 @@
       <c r="J98" t="n">
         <v>1.048</v>
       </c>
+      <c r="K98" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M98" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="N98" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="O98" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="P98" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="R98" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="S98" t="n">
+        <v>312.07</v>
+      </c>
+      <c r="T98" t="n">
+        <v>356.72</v>
+      </c>
+      <c r="U98" t="n">
+        <v>22</v>
+      </c>
+      <c r="V98" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4387,6 +7939,42 @@
       <c r="J99" t="n">
         <v>1.048</v>
       </c>
+      <c r="K99" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M99" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="P99" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="S99" t="n">
+        <v>263.72</v>
+      </c>
+      <c r="T99" t="n">
+        <v>259.69</v>
+      </c>
+      <c r="U99" t="n">
+        <v>18</v>
+      </c>
+      <c r="V99" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4427,6 +8015,42 @@
       <c r="J100" t="n">
         <v>1.048</v>
       </c>
+      <c r="K100" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M100" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="O100" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="P100" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="S100" t="n">
+        <v>212.16</v>
+      </c>
+      <c r="T100" t="n">
+        <v>297.99</v>
+      </c>
+      <c r="U100" t="n">
+        <v>14</v>
+      </c>
+      <c r="V100" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4467,6 +8091,42 @@
       <c r="J101" t="n">
         <v>1.048</v>
       </c>
+      <c r="K101" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M101" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O101" t="n">
+        <v>-3.89</v>
+      </c>
+      <c r="P101" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="S101" t="n">
+        <v>230.37</v>
+      </c>
+      <c r="T101" t="n">
+        <v>343.2</v>
+      </c>
+      <c r="U101" t="n">
+        <v>12</v>
+      </c>
+      <c r="V101" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4507,6 +8167,42 @@
       <c r="J102" t="n">
         <v>1.052</v>
       </c>
+      <c r="K102" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M102" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="N102" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O102" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P102" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R102" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="S102" t="n">
+        <v>448.12</v>
+      </c>
+      <c r="T102" t="n">
+        <v>385.15</v>
+      </c>
+      <c r="U102" t="n">
+        <v>30</v>
+      </c>
+      <c r="V102" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4547,6 +8243,42 @@
       <c r="J103" t="n">
         <v>1.052</v>
       </c>
+      <c r="K103" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M103" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="N103" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O103" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P103" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="R103" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="S103" t="n">
+        <v>446.27</v>
+      </c>
+      <c r="T103" t="n">
+        <v>345.52</v>
+      </c>
+      <c r="U103" t="n">
+        <v>30</v>
+      </c>
+      <c r="V103" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4587,6 +8319,42 @@
       <c r="J104" t="n">
         <v>1.052</v>
       </c>
+      <c r="K104" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M104" t="n">
+        <v>80</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="O104" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="P104" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="S104" t="n">
+        <v>370.5</v>
+      </c>
+      <c r="T104" t="n">
+        <v>334.55</v>
+      </c>
+      <c r="U104" t="n">
+        <v>21</v>
+      </c>
+      <c r="V104" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4627,6 +8395,42 @@
       <c r="J105" t="n">
         <v>1.052</v>
       </c>
+      <c r="K105" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M105" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="O105" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="P105" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="R105" t="n">
+        <v>1</v>
+      </c>
+      <c r="S105" t="n">
+        <v>346.37</v>
+      </c>
+      <c r="T105" t="n">
+        <v>376.55</v>
+      </c>
+      <c r="U105" t="n">
+        <v>23</v>
+      </c>
+      <c r="V105" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4667,6 +8471,42 @@
       <c r="J106" t="n">
         <v>1.052</v>
       </c>
+      <c r="K106" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M106" t="n">
+        <v>60</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="O106" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="P106" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="S106" t="n">
+        <v>362.32</v>
+      </c>
+      <c r="T106" t="n">
+        <v>380.79</v>
+      </c>
+      <c r="U106" t="n">
+        <v>18</v>
+      </c>
+      <c r="V106" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4707,6 +8547,42 @@
       <c r="J107" t="n">
         <v>1.052</v>
       </c>
+      <c r="K107" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M107" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="N107" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P107" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="R107" t="n">
+        <v>1</v>
+      </c>
+      <c r="S107" t="n">
+        <v>401.35</v>
+      </c>
+      <c r="T107" t="n">
+        <v>382.98</v>
+      </c>
+      <c r="U107" t="n">
+        <v>22</v>
+      </c>
+      <c r="V107" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4747,6 +8623,42 @@
       <c r="J108" t="n">
         <v>1.052</v>
       </c>
+      <c r="K108" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M108" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="O108" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P108" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="S108" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="T108" t="n">
+        <v>367.62</v>
+      </c>
+      <c r="U108" t="n">
+        <v>25</v>
+      </c>
+      <c r="V108" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4787,6 +8699,42 @@
       <c r="J109" t="n">
         <v>1.052</v>
       </c>
+      <c r="K109" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M109" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="O109" t="n">
+        <v>-2.45</v>
+      </c>
+      <c r="P109" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R109" t="n">
+        <v>1</v>
+      </c>
+      <c r="S109" t="n">
+        <v>383.78</v>
+      </c>
+      <c r="T109" t="n">
+        <v>469.46</v>
+      </c>
+      <c r="U109" t="n">
+        <v>20</v>
+      </c>
+      <c r="V109" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4827,6 +8775,42 @@
       <c r="J110" t="n">
         <v>1.052</v>
       </c>
+      <c r="K110" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M110" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="O110" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="P110" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="S110" t="n">
+        <v>313.31</v>
+      </c>
+      <c r="T110" t="n">
+        <v>350.07</v>
+      </c>
+      <c r="U110" t="n">
+        <v>23</v>
+      </c>
+      <c r="V110" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4867,6 +8851,42 @@
       <c r="J111" t="n">
         <v>1.052</v>
       </c>
+      <c r="K111" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M111" t="n">
+        <v>60</v>
+      </c>
+      <c r="N111" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O111" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="P111" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="R111" t="n">
+        <v>1</v>
+      </c>
+      <c r="S111" t="n">
+        <v>320.57</v>
+      </c>
+      <c r="T111" t="n">
+        <v>403.42</v>
+      </c>
+      <c r="U111" t="n">
+        <v>22</v>
+      </c>
+      <c r="V111" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4899,13 +8919,49 @@
         <v>1.59</v>
       </c>
       <c r="H112" t="n">
-        <v>1.24</v>
+        <v>1.238</v>
       </c>
       <c r="I112" t="n">
         <v>24</v>
       </c>
       <c r="J112" t="n">
-        <v>1.093</v>
+        <v>1.092</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M112" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="N112" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="O112" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="P112" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R112" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="S112" t="n">
+        <v>348.41</v>
+      </c>
+      <c r="T112" t="n">
+        <v>210.51</v>
+      </c>
+      <c r="U112" t="n">
+        <v>20</v>
+      </c>
+      <c r="V112" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="113">
@@ -4939,13 +8995,49 @@
         <v>1.34</v>
       </c>
       <c r="H113" t="n">
-        <v>1.24</v>
+        <v>1.238</v>
       </c>
       <c r="I113" t="n">
         <v>24</v>
       </c>
       <c r="J113" t="n">
-        <v>1.093</v>
+        <v>1.092</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M113" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="N113" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P113" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="R113" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="S113" t="n">
+        <v>261.8</v>
+      </c>
+      <c r="T113" t="n">
+        <v>244.9</v>
+      </c>
+      <c r="U113" t="n">
+        <v>20</v>
+      </c>
+      <c r="V113" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="114">
@@ -4976,16 +9068,52 @@
         <v>2</v>
       </c>
       <c r="G114" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="H114" t="n">
-        <v>1.24</v>
+        <v>1.238</v>
       </c>
       <c r="I114" t="n">
         <v>24</v>
       </c>
       <c r="J114" t="n">
-        <v>1.093</v>
+        <v>1.092</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M114" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="N114" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="O114" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="P114" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="S114" t="n">
+        <v>262.01</v>
+      </c>
+      <c r="T114" t="n">
+        <v>294.27</v>
+      </c>
+      <c r="U114" t="n">
+        <v>21</v>
+      </c>
+      <c r="V114" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="115">
@@ -5019,13 +9147,49 @@
         <v>1.14</v>
       </c>
       <c r="H115" t="n">
-        <v>1.24</v>
+        <v>1.238</v>
       </c>
       <c r="I115" t="n">
         <v>24</v>
       </c>
       <c r="J115" t="n">
-        <v>1.093</v>
+        <v>1.092</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M115" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="O115" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="P115" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="S115" t="n">
+        <v>240.16</v>
+      </c>
+      <c r="T115" t="n">
+        <v>194.74</v>
+      </c>
+      <c r="U115" t="n">
+        <v>18</v>
+      </c>
+      <c r="V115" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="116">
@@ -5059,13 +9223,49 @@
         <v>0.87</v>
       </c>
       <c r="H116" t="n">
-        <v>1.24</v>
+        <v>1.238</v>
       </c>
       <c r="I116" t="n">
         <v>24</v>
       </c>
       <c r="J116" t="n">
-        <v>1.093</v>
+        <v>1.092</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M116" t="n">
+        <v>75</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="O116" t="n">
+        <v>-2.96</v>
+      </c>
+      <c r="P116" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="S116" t="n">
+        <v>148</v>
+      </c>
+      <c r="T116" t="n">
+        <v>219.01</v>
+      </c>
+      <c r="U116" t="n">
+        <v>10</v>
+      </c>
+      <c r="V116" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="117">
@@ -5105,7 +9305,43 @@
         <v>24</v>
       </c>
       <c r="J117" t="n">
-        <v>1.093</v>
+        <v>1.092</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M117" t="n">
+        <v>75</v>
+      </c>
+      <c r="N117" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="O117" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="P117" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="R117" t="n">
+        <v>1.273</v>
+      </c>
+      <c r="S117" t="n">
+        <v>295.31</v>
+      </c>
+      <c r="T117" t="n">
+        <v>205.84</v>
+      </c>
+      <c r="U117" t="n">
+        <v>22</v>
+      </c>
+      <c r="V117" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="118">
@@ -5145,7 +9381,43 @@
         <v>24</v>
       </c>
       <c r="J118" t="n">
-        <v>1.093</v>
+        <v>1.092</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M118" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N118" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O118" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="P118" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R118" t="n">
+        <v>1.364</v>
+      </c>
+      <c r="S118" t="n">
+        <v>319.36</v>
+      </c>
+      <c r="T118" t="n">
+        <v>264.44</v>
+      </c>
+      <c r="U118" t="n">
+        <v>22</v>
+      </c>
+      <c r="V118" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="119">
@@ -5185,7 +9457,43 @@
         <v>24</v>
       </c>
       <c r="J119" t="n">
-        <v>1.093</v>
+        <v>1.092</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M119" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O119" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="P119" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="S119" t="n">
+        <v>209.04</v>
+      </c>
+      <c r="T119" t="n">
+        <v>230.13</v>
+      </c>
+      <c r="U119" t="n">
+        <v>14</v>
+      </c>
+      <c r="V119" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="120">
@@ -5225,7 +9533,43 @@
         <v>24</v>
       </c>
       <c r="J120" t="n">
-        <v>1.093</v>
+        <v>1.092</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M120" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O120" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="P120" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="R120" t="n">
+        <v>1</v>
+      </c>
+      <c r="S120" t="n">
+        <v>194.59</v>
+      </c>
+      <c r="T120" t="n">
+        <v>301.76</v>
+      </c>
+      <c r="U120" t="n">
+        <v>12</v>
+      </c>
+      <c r="V120" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="121">
@@ -5265,7 +9609,43 @@
         <v>24</v>
       </c>
       <c r="J121" t="n">
-        <v>1.093</v>
+        <v>1.092</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M121" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>-4.71</v>
+      </c>
+      <c r="P121" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="S121" t="n">
+        <v>145.15</v>
+      </c>
+      <c r="T121" t="n">
+        <v>258.13</v>
+      </c>
+      <c r="U121" t="n">
+        <v>6</v>
+      </c>
+      <c r="V121" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="122">
@@ -5307,6 +9687,42 @@
       <c r="J122" t="n">
         <v>1.099</v>
       </c>
+      <c r="K122" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M122" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="N122" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="O122" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="P122" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R122" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="S122" t="n">
+        <v>390.13</v>
+      </c>
+      <c r="T122" t="n">
+        <v>335.58</v>
+      </c>
+      <c r="U122" t="n">
+        <v>26</v>
+      </c>
+      <c r="V122" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5347,6 +9763,42 @@
       <c r="J123" t="n">
         <v>1.099</v>
       </c>
+      <c r="K123" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M123" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="P123" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R123" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="S123" t="n">
+        <v>306.89</v>
+      </c>
+      <c r="T123" t="n">
+        <v>298.85</v>
+      </c>
+      <c r="U123" t="n">
+        <v>23</v>
+      </c>
+      <c r="V123" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5387,6 +9839,42 @@
       <c r="J124" t="n">
         <v>1.099</v>
       </c>
+      <c r="K124" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M124" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="O124" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P124" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="S124" t="n">
+        <v>256.44</v>
+      </c>
+      <c r="T124" t="n">
+        <v>207.84</v>
+      </c>
+      <c r="U124" t="n">
+        <v>18</v>
+      </c>
+      <c r="V124" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5427,6 +9915,42 @@
       <c r="J125" t="n">
         <v>1.099</v>
       </c>
+      <c r="K125" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M125" t="n">
+        <v>69</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="O125" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="P125" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="S125" t="n">
+        <v>305.37</v>
+      </c>
+      <c r="T125" t="n">
+        <v>249.61</v>
+      </c>
+      <c r="U125" t="n">
+        <v>19</v>
+      </c>
+      <c r="V125" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5467,6 +9991,42 @@
       <c r="J126" t="n">
         <v>1.099</v>
       </c>
+      <c r="K126" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M126" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="O126" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="P126" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>220.83</v>
+      </c>
+      <c r="T126" t="n">
+        <v>262.29</v>
+      </c>
+      <c r="U126" t="n">
+        <v>15</v>
+      </c>
+      <c r="V126" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5507,6 +10067,42 @@
       <c r="J127" t="n">
         <v>1.099</v>
       </c>
+      <c r="K127" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M127" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="N127" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="O127" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="P127" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R127" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="S127" t="n">
+        <v>408.84</v>
+      </c>
+      <c r="T127" t="n">
+        <v>264.07</v>
+      </c>
+      <c r="U127" t="n">
+        <v>22</v>
+      </c>
+      <c r="V127" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5547,6 +10143,42 @@
       <c r="J128" t="n">
         <v>1.099</v>
       </c>
+      <c r="K128" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M128" t="n">
+        <v>69</v>
+      </c>
+      <c r="N128" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O128" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P128" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R128" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="S128" t="n">
+        <v>365.97</v>
+      </c>
+      <c r="T128" t="n">
+        <v>277.41</v>
+      </c>
+      <c r="U128" t="n">
+        <v>26</v>
+      </c>
+      <c r="V128" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5587,6 +10219,42 @@
       <c r="J129" t="n">
         <v>1.099</v>
       </c>
+      <c r="K129" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M129" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="N129" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O129" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="P129" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R129" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="S129" t="n">
+        <v>274.81</v>
+      </c>
+      <c r="T129" t="n">
+        <v>297.49</v>
+      </c>
+      <c r="U129" t="n">
+        <v>27</v>
+      </c>
+      <c r="V129" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5627,6 +10295,42 @@
       <c r="J130" t="n">
         <v>1.099</v>
       </c>
+      <c r="K130" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M130" t="n">
+        <v>69</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="O130" t="n">
+        <v>-5.15</v>
+      </c>
+      <c r="P130" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="S130" t="n">
+        <v>212.05</v>
+      </c>
+      <c r="T130" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="U130" t="n">
+        <v>16</v>
+      </c>
+      <c r="V130" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5667,6 +10371,42 @@
       <c r="J131" t="n">
         <v>1.099</v>
       </c>
+      <c r="K131" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M131" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O131" t="n">
+        <v>-6.44</v>
+      </c>
+      <c r="P131" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="S131" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="T131" t="n">
+        <v>279.31</v>
+      </c>
+      <c r="U131" t="n">
+        <v>8</v>
+      </c>
+      <c r="V131" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5696,7 +10436,7 @@
         <v>5</v>
       </c>
       <c r="G132" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H132" t="n">
         <v>1.19</v>
@@ -5707,6 +10447,42 @@
       <c r="J132" t="n">
         <v>1.072</v>
       </c>
+      <c r="K132" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M132" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="N132" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="O132" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="P132" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R132" t="n">
+        <v>1</v>
+      </c>
+      <c r="S132" t="n">
+        <v>237.01</v>
+      </c>
+      <c r="T132" t="n">
+        <v>117.91</v>
+      </c>
+      <c r="U132" t="n">
+        <v>16</v>
+      </c>
+      <c r="V132" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5747,6 +10523,42 @@
       <c r="J133" t="n">
         <v>1.072</v>
       </c>
+      <c r="K133" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M133" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N133" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O133" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="P133" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R133" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="S133" t="n">
+        <v>274.2</v>
+      </c>
+      <c r="T133" t="n">
+        <v>160.39</v>
+      </c>
+      <c r="U133" t="n">
+        <v>17</v>
+      </c>
+      <c r="V133" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5787,6 +10599,42 @@
       <c r="J134" t="n">
         <v>1.072</v>
       </c>
+      <c r="K134" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M134" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="O134" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="P134" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="R134" t="n">
+        <v>1</v>
+      </c>
+      <c r="S134" t="n">
+        <v>261.06</v>
+      </c>
+      <c r="T134" t="n">
+        <v>196.24</v>
+      </c>
+      <c r="U134" t="n">
+        <v>15</v>
+      </c>
+      <c r="V134" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5827,6 +10675,42 @@
       <c r="J135" t="n">
         <v>1.072</v>
       </c>
+      <c r="K135" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M135" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="P135" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="S135" t="n">
+        <v>202.24</v>
+      </c>
+      <c r="T135" t="n">
+        <v>209.73</v>
+      </c>
+      <c r="U135" t="n">
+        <v>15</v>
+      </c>
+      <c r="V135" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5856,7 +10740,7 @@
         <v>5</v>
       </c>
       <c r="G136" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="H136" t="n">
         <v>1.19</v>
@@ -5867,6 +10751,42 @@
       <c r="J136" t="n">
         <v>1.072</v>
       </c>
+      <c r="K136" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M136" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="O136" t="n">
+        <v>-3.15</v>
+      </c>
+      <c r="P136" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="S136" t="n">
+        <v>176.99</v>
+      </c>
+      <c r="T136" t="n">
+        <v>243.14</v>
+      </c>
+      <c r="U136" t="n">
+        <v>11</v>
+      </c>
+      <c r="V136" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5907,6 +10827,42 @@
       <c r="J137" t="n">
         <v>1.072</v>
       </c>
+      <c r="K137" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M137" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N137" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="P137" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R137" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="S137" t="n">
+        <v>176.71</v>
+      </c>
+      <c r="T137" t="n">
+        <v>162.33</v>
+      </c>
+      <c r="U137" t="n">
+        <v>16</v>
+      </c>
+      <c r="V137" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5947,6 +10903,42 @@
       <c r="J138" t="n">
         <v>1.072</v>
       </c>
+      <c r="K138" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M138" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="N138" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O138" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="P138" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S138" t="n">
+        <v>234.05</v>
+      </c>
+      <c r="T138" t="n">
+        <v>250.54</v>
+      </c>
+      <c r="U138" t="n">
+        <v>16</v>
+      </c>
+      <c r="V138" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5987,6 +10979,42 @@
       <c r="J139" t="n">
         <v>1.072</v>
       </c>
+      <c r="K139" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M139" t="n">
+        <v>81</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="P139" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="R139" t="n">
+        <v>1</v>
+      </c>
+      <c r="S139" t="n">
+        <v>205.43</v>
+      </c>
+      <c r="T139" t="n">
+        <v>197.68</v>
+      </c>
+      <c r="U139" t="n">
+        <v>13</v>
+      </c>
+      <c r="V139" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6027,6 +11055,42 @@
       <c r="J140" t="n">
         <v>1.072</v>
       </c>
+      <c r="K140" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M140" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O140" t="n">
+        <v>-4.18</v>
+      </c>
+      <c r="P140" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="S140" t="n">
+        <v>171.92</v>
+      </c>
+      <c r="T140" t="n">
+        <v>259.63</v>
+      </c>
+      <c r="U140" t="n">
+        <v>7</v>
+      </c>
+      <c r="V140" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6067,6 +11131,42 @@
       <c r="J141" t="n">
         <v>1.072</v>
       </c>
+      <c r="K141" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M141" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="O141" t="n">
+        <v>-6.77</v>
+      </c>
+      <c r="P141" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="R141" t="n">
+        <v>1</v>
+      </c>
+      <c r="S141" t="n">
+        <v>139.22</v>
+      </c>
+      <c r="T141" t="n">
+        <v>281.39</v>
+      </c>
+      <c r="U141" t="n">
+        <v>8</v>
+      </c>
+      <c r="V141" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6107,6 +11207,42 @@
       <c r="J142" t="n">
         <v>1.05</v>
       </c>
+      <c r="K142" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M142" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="N142" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="O142" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="P142" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R142" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="S142" t="n">
+        <v>232.03</v>
+      </c>
+      <c r="T142" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="U142" t="n">
+        <v>16</v>
+      </c>
+      <c r="V142" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6147,6 +11283,42 @@
       <c r="J143" t="n">
         <v>1.05</v>
       </c>
+      <c r="K143" t="n">
+        <v>1</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M143" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="N143" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="O143" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P143" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R143" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="S143" t="n">
+        <v>221.93</v>
+      </c>
+      <c r="T143" t="n">
+        <v>156.49</v>
+      </c>
+      <c r="U143" t="n">
+        <v>17</v>
+      </c>
+      <c r="V143" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6187,6 +11359,42 @@
       <c r="J144" t="n">
         <v>1.05</v>
       </c>
+      <c r="K144" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M144" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="N144" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="O144" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="P144" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="S144" t="n">
+        <v>168.78</v>
+      </c>
+      <c r="T144" t="n">
+        <v>101.42</v>
+      </c>
+      <c r="U144" t="n">
+        <v>13</v>
+      </c>
+      <c r="V144" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6227,6 +11435,42 @@
       <c r="J145" t="n">
         <v>1.05</v>
       </c>
+      <c r="K145" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M145" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="N145" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O145" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="P145" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="S145" t="n">
+        <v>137.92</v>
+      </c>
+      <c r="T145" t="n">
+        <v>110.11</v>
+      </c>
+      <c r="U145" t="n">
+        <v>12</v>
+      </c>
+      <c r="V145" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6267,6 +11511,42 @@
       <c r="J146" t="n">
         <v>1.05</v>
       </c>
+      <c r="K146" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M146" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="O146" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="P146" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="S146" t="n">
+        <v>174.8</v>
+      </c>
+      <c r="T146" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="U146" t="n">
+        <v>8</v>
+      </c>
+      <c r="V146" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6307,6 +11587,42 @@
       <c r="J147" t="n">
         <v>1.05</v>
       </c>
+      <c r="K147" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M147" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O147" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P147" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="R147" t="n">
+        <v>1</v>
+      </c>
+      <c r="S147" t="n">
+        <v>166.56</v>
+      </c>
+      <c r="T147" t="n">
+        <v>175.06</v>
+      </c>
+      <c r="U147" t="n">
+        <v>10</v>
+      </c>
+      <c r="V147" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6347,6 +11663,42 @@
       <c r="J148" t="n">
         <v>1.05</v>
       </c>
+      <c r="K148" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M148" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="N148" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="O148" t="n">
+        <v>-2.17</v>
+      </c>
+      <c r="P148" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="R148" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S148" t="n">
+        <v>149.03</v>
+      </c>
+      <c r="T148" t="n">
+        <v>186</v>
+      </c>
+      <c r="U148" t="n">
+        <v>7</v>
+      </c>
+      <c r="V148" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6387,6 +11739,42 @@
       <c r="J149" t="n">
         <v>1.05</v>
       </c>
+      <c r="K149" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M149" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="O149" t="n">
+        <v>-7.23</v>
+      </c>
+      <c r="P149" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S149" t="n">
+        <v>95.53</v>
+      </c>
+      <c r="T149" t="n">
+        <v>218.37</v>
+      </c>
+      <c r="U149" t="n">
+        <v>7</v>
+      </c>
+      <c r="V149" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6427,6 +11815,42 @@
       <c r="J150" t="n">
         <v>1.05</v>
       </c>
+      <c r="K150" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M150" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="N150" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="O150" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="P150" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S150" t="n">
+        <v>99.61</v>
+      </c>
+      <c r="T150" t="n">
+        <v>158.2</v>
+      </c>
+      <c r="U150" t="n">
+        <v>6</v>
+      </c>
+      <c r="V150" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6466,6 +11890,42 @@
       </c>
       <c r="J151" t="n">
         <v>1.05</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M151" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="N151" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="O151" t="n">
+        <v>-6.31</v>
+      </c>
+      <c r="P151" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="R151" t="n">
+        <v>1</v>
+      </c>
+      <c r="S151" t="n">
+        <v>90.59</v>
+      </c>
+      <c r="T151" t="n">
+        <v>197.78</v>
+      </c>
+      <c r="U151" t="n">
+        <v>8</v>
+      </c>
+      <c r="V151" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
